--- a/RESULTADOS.xlsx
+++ b/RESULTADOS.xlsx
@@ -1,25 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTUDIO\Downloads\TP-IO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1019D43-3347-4AC3-B7A2-FCF292AB6F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="RESULTADOS ENVIOS (X)" sheetId="1" r:id="rId1"/>
+    <sheet name="RESULTADOS PRODUCCION (Y)" sheetId="2" r:id="rId2"/>
+    <sheet name="RESULTADOS ENVIOS A SF (LD)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="CANTIDAD_A_ENVIAR" comment="Resultados del solver para X. Representa la cantida del producti I que debe enviarse de la planta J al centro K para que la FO sea optima.">'RESULTADOS ENVIOS (X)'!$D$2:$D$97</definedName>
+    <definedName name="LECHE_DESCREMADA_ENVIADA_A_SANTA_FE" comment="Resultados del solver para LD. Expresa la cantidad de leche descremada que la planta J envia a la planta de Santa Fe.">'RESULTADOS ENVIOS A SF (LD)'!$C$2:$C$3</definedName>
+    <definedName name="LECHE_PROCESADA" comment="Resultados del solver para Y. Expresa la cantidad de leche equivalente que fue procesada en cada planta.">'RESULTADOS PRODUCCION (Y)'!$C$2:$C$4</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="25">
+  <si>
+    <t>PRODUCTO</t>
+  </si>
+  <si>
+    <t>PLANTA</t>
+  </si>
+  <si>
+    <t>CENTROS</t>
+  </si>
+  <si>
+    <t>LFE</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>LFD</t>
+  </si>
+  <si>
+    <t>LPE</t>
+  </si>
+  <si>
+    <t>LPD</t>
+  </si>
+  <si>
+    <t>CREMA</t>
+  </si>
+  <si>
+    <t>MANTECA</t>
+  </si>
+  <si>
+    <t>QB</t>
+  </si>
+  <si>
+    <t>QMB</t>
+  </si>
+  <si>
+    <t>CANTIDAD_A_ENVIAR</t>
+  </si>
+  <si>
+    <t>LECHE_PROCESADA</t>
+  </si>
+  <si>
+    <t>LUGAR</t>
+  </si>
+  <si>
+    <t>BUENOS AIRES</t>
+  </si>
+  <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>LECHE_DESCREMADA_ENVIADA_A_SANTA_FE</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -37,7 +139,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -45,12 +147,181 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +601,1479 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D97"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6">
+        <v>546191.91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8">
+        <v>218476.764</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="11">
+        <v>145651.17600000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="8">
+        <v>303439.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="6">
+        <v>281371.58999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="8">
+        <v>112548.63599999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="11">
+        <v>75032.423999999985</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="8">
+        <v>156317.54999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="6">
+        <v>39919.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="8">
+        <v>15967.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="11">
+        <v>10645.199999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="8">
+        <v>22177.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="6">
+        <v>114608.30437959186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="8">
+        <v>5450.0579999999991</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="11">
+        <v>3633.3719999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="8">
+        <v>7569.5249999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="6">
+        <v>96808.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="8">
+        <v>38723.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="8">
+        <v>53782.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="11">
+        <v>25815.599999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="6">
+        <v>17995.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="8">
+        <v>9997.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="8">
+        <v>7198.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="11">
+        <v>4798.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="6">
+        <v>218609.55000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="8">
+        <v>87443.819999999992</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="11">
+        <v>58295.88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="8">
+        <v>121449.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="6">
+        <v>70333.24500000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="8">
+        <v>28133.297999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="11">
+        <v>18755.531999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="8">
+        <v>39074.025000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05649807-5BCA-4CDC-892B-C264250D9331}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="15">
+        <v>4480622.5343550006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="15">
+        <v>2262609.3395699998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="15">
+        <v>1490206.4079749999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85634DFB-2640-45DB-972B-03B088998E42}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="15">
+        <v>89559.050968955693</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="15">
+        <v>153989.61968015059</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/RESULTADOS.xlsx
+++ b/RESULTADOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTUDIO\Downloads\TP-IO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frsfutneduar-my.sharepoint.com/personal/lzeballos_frsf_utn_edu_ar/Documents/Escritorio/Facultad/io/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1019D43-3347-4AC3-B7A2-FCF292AB6F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESULTADOS ENVIOS (X)" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="LECHE_DESCREMADA_ENVIADA_A_SANTA_FE" comment="Resultados del solver para LD. Expresa la cantidad de leche descremada que la planta J envia a la planta de Santa Fe.">'RESULTADOS ENVIOS A SF (LD)'!$C$2:$C$3</definedName>
     <definedName name="LECHE_PROCESADA" comment="Resultados del solver para Y. Expresa la cantidad de leche equivalente que fue procesada en cada planta.">'RESULTADOS PRODUCCION (Y)'!$C$2:$C$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -603,14 +603,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D97"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,7 +624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -638,7 +638,7 @@
         <v>546191.91</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
@@ -680,7 +680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
@@ -694,7 +694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>3</v>
       </c>
@@ -722,7 +722,7 @@
         <v>218476.764</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>3</v>
       </c>
@@ -736,7 +736,7 @@
         <v>145651.17600000001</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>3</v>
       </c>
@@ -764,7 +764,7 @@
         <v>303439.95</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>3</v>
       </c>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>3</v>
       </c>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>11</v>
       </c>
@@ -806,7 +806,7 @@
         <v>281371.58999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>11</v>
       </c>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>11</v>
       </c>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>11</v>
       </c>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>11</v>
       </c>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>11</v>
       </c>
@@ -890,7 +890,7 @@
         <v>112548.63599999998</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>11</v>
       </c>
@@ -904,7 +904,7 @@
         <v>75032.423999999985</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>11</v>
       </c>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>11</v>
       </c>
@@ -932,7 +932,7 @@
         <v>156317.54999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>11</v>
       </c>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>11</v>
       </c>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>12</v>
       </c>
@@ -974,7 +974,7 @@
         <v>39919.5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>12</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>12</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>12</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>12</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>12</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>12</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>15967.8</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>12</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>10645.199999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>12</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>12</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>22177.5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>12</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>12</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>13</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>114608.30437959186</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>13</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>13</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>13</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>13</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>13</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>13</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>5450.0579999999991</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>13</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>3633.3719999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>13</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>13</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>7569.5249999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>13</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>13</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>14</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>96808.5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>14</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>14</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>14</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>14</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>14</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>14</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>38723.4</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>14</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>14</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>14</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>53782.5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>14</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
         <v>14</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>25815.599999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>15</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>17995.5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>15</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>15</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>15</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>15</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>15</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>15</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>15</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>15</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>9997.5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>15</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>7198.2</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>15</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>4798.8</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>16</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>218609.55000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>16</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>16</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>16</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>16</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>16</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>16</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>87443.819999999992</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>16</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>58295.88</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>16</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>16</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>121449.75</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>16</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
         <v>16</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>17</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>70333.24500000001</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>17</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>17</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>17</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
         <v>17</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
         <v>17</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
         <v>17</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>28133.297999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
         <v>17</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>18755.531999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
         <v>17</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
         <v>17</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>39074.025000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
         <v>17</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
         <v>17</v>
       </c>
@@ -1976,12 +1976,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05649807-5BCA-4CDC-892B-C264250D9331}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="18.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>4480622.5343550006</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>2262609.3395699998</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -2033,14 +2033,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85634DFB-2640-45DB-972B-03B088998E42}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>89559.050968955693</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
